--- a/MonteCarloApp/simulaciones/resultados/Secuencial_C++_metricas.xlsx
+++ b/MonteCarloApp/simulaciones/resultados/Secuencial_C++_metricas.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08694362640380859</v>
+        <v>0.9457728862762451</v>
       </c>
       <c r="C2" t="n">
-        <v>155.4609375</v>
+        <v>152.2109375</v>
       </c>
       <c r="D2" t="n">
-        <v>10.3</v>
+        <v>10.8</v>
       </c>
     </row>
   </sheetData>
